--- a/Checklists.xlsx
+++ b/Checklists.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A65132-DC41-4DA6-B7BF-B89C9FFEB700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DFE48F5-DD9B-4926-A5A2-8A60236108B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="117">
   <si>
     <t>Формат</t>
   </si>
@@ -384,6 +384,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
       <t xml:space="preserve">1. Go to </t>
     </r>
     <r>
@@ -392,19 +397,17 @@
         <sz val="10"/>
         <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
       </rPr>
-      <t>https://best.aliexpress.com/</t>
+      <t xml:space="preserve">https://best.aliexpress.com/
+</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">
-2. Go to Account &gt; Register button
+      <t>2. Go to Account &gt; Register button
 3. Choose a location
 4. Input email from test data
 5. Input a password (6-20 symbols)
@@ -429,33 +432,12 @@
 10. The user is logged out
 11. The user is logged in without error messages</t>
   </si>
-  <si>
-    <t>РЕКОМЕНДАЦИИ</t>
-  </si>
-  <si>
-    <t>ID присваивается TMS системой автоматически. Не надо писать номер в названии кейса</t>
-  </si>
-  <si>
-    <t>Заголовок кейса должен отражать суть проверки. Например, если это регистрация, то с какими данными и с помощью какого мехаизма</t>
-  </si>
-  <si>
-    <t>Действия, которые нужно сделать до запуска кейса. Полезный атрибут, который помогает сократить количество шагов. Например, создание юзера или предварительная регистрация.
-Так же существуют и постусловия (Post-conditions), если нужно сделать какие-то действия после запуска кейса. Например, удаление тестовых юзеров или данных</t>
-  </si>
-  <si>
-    <t>В зависимости от сложности и объема задачи в шагах может быть разное количество кейсов. Оптимально - до 10. Если ваш кейс получается на 20 шагов и больше, то его можно оптимизировать. Например, объединить несколько шагов. Также следует помнить о том, что один кейс- одна проверка. Если их больше, то лучше создать тестовый набор
-Также помните о том, что иногда можно объединять кейсы, если время ограничено. Но это касается только ПОЗИТИВНЫХ проверок. Негативные проверки нужно тестировать по отдельности, иначе будут сложно локализовать дефект, если он будет и вы потратите лишнее время</t>
-  </si>
-  <si>
-    <t>Стандартно для каждого шага в кейсе должен быть свой ожидаемый результат. Но существует и другой подход, когда есть один общий ожидаемый результат для кейса. Для выполнения домашних заданий и реальных ТЗ, советую делать все-таки ОР для каждого шага, а уже придя на проект возможно вам повезет и он будет всего один
-Также одной из хороших практик является добавление скринов для некоторых ОР в кейсах, но это ждет вас уже на крупных проектах. Сейчас от вас это не требуется и опять же не всегда применяется из-за отсутствия времени</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,33 +459,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,14 +554,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -667,33 +633,7 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -706,9 +646,7 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -721,74 +659,14 @@
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -796,15 +674,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -837,26 +706,17 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
@@ -864,26 +724,23 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,107 +1331,107 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="28" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="12">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="9">
         <v>45997</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="11"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="28" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="28" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:9" ht="24">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="28" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="24">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="5" t="s">
@@ -1582,881 +1439,873 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="E8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="14" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="31"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="14" t="s">
+      <c r="A10" s="23"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="E10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="E11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="E12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="E13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="14" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="E14" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="31"/>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="E15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="31"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="14" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="E16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="31"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="14" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="E17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="31"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="14" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="E18" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="31"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="14" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="E19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="31"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="14" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="E20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="31"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="14" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="E21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="24">
-      <c r="A22" s="31"/>
-      <c r="B22" s="32" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="E22" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="31"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="14" t="s">
+      <c r="A23" s="23"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="E23" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="24">
-      <c r="A24" s="31"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="14" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="E24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="31"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="14" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="E25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="24">
-      <c r="A26" s="31"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="14" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="E26" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="24">
-      <c r="A27" s="31"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="14" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="E27" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="31"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="14" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="E28" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="24">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="14" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="E29" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="14" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="E30" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="31"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="14" t="s">
+      <c r="A31" s="23"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="E31" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="31"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="14" t="s">
+      <c r="A32" s="23"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="E32" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="31"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="14" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="E33" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="31"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="14" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="E34" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="31"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="30" t="s">
+      <c r="A35" s="23"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="E35" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="31"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="14" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="E36" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="31"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="14" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="E37" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="31"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="14" t="s">
+      <c r="A38" s="23"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E38" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="E38" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="14" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E39" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="E39" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="31"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="14" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="E40" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="24">
-      <c r="A41" s="31"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="14" t="s">
+      <c r="A41" s="23"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+      <c r="E41" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="31"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="14" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="E42" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="24">
-      <c r="A43" s="31"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="14" t="s">
+      <c r="A43" s="23"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="E43" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="24">
-      <c r="A44" s="31"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="14" t="s">
+      <c r="A44" s="23"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="E44" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="31"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="14" t="s">
+      <c r="A45" s="23"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="E45" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="31"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="14" t="s">
+      <c r="A46" s="23"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+      <c r="E46" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="14" t="s">
+      <c r="A47" s="23"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="E47" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="31"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="14" t="s">
+      <c r="A48" s="23"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="E48" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="31"/>
-      <c r="B49" s="32" t="s">
+      <c r="A49" s="23"/>
+      <c r="B49" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+      <c r="E49" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="24">
-      <c r="A50" s="31"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="14" t="s">
+      <c r="A50" s="23"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+      <c r="E50" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
     </row>
     <row r="51" spans="1:8" ht="24">
-      <c r="A51" s="31"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="14" t="s">
+      <c r="A51" s="23"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E51" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+      <c r="E51" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="31"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="30" t="s">
+      <c r="A52" s="23"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E52" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="E52" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
     </row>
     <row r="53" spans="1:8" ht="24">
-      <c r="A53" s="31"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="14" t="s">
+      <c r="A53" s="23"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E53" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+      <c r="E53" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="31"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="30" t="s">
+      <c r="A54" s="23"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E54" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+      <c r="E54" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
     </row>
     <row r="55" spans="1:8" ht="24">
-      <c r="A55" s="31"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="14" t="s">
+      <c r="A55" s="23"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E55" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="E55" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="31"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="30" t="s">
+      <c r="A56" s="23"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="E56" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
     </row>
     <row r="57" spans="1:8" ht="24">
-      <c r="A57" s="31"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="14" t="s">
+      <c r="A57" s="23"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+      <c r="E57" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="31"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="30" t="s">
+      <c r="A58" s="23"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E58" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+      <c r="E58" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
     </row>
     <row r="59" spans="1:8" ht="24">
-      <c r="A59" s="31"/>
-      <c r="B59" s="32"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="14" t="s">
+      <c r="A59" s="23"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E59" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="E59" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="31"/>
-      <c r="B60" s="32"/>
-      <c r="C60" s="30" t="s">
+      <c r="A60" s="23"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E60" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+      <c r="E60" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="24">
-      <c r="A61" s="31"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="14" t="s">
+      <c r="A61" s="23"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E61" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+      <c r="E61" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="31"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="27" t="s">
+      <c r="A62" s="23"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E62" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="E62" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
     </row>
     <row r="63" spans="1:8" ht="24">
-      <c r="A63" s="31"/>
-      <c r="B63" s="32" t="s">
+      <c r="A63" s="23"/>
+      <c r="B63" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="30" t="s">
+      <c r="C63" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E63" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="E63" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="31"/>
-      <c r="B64" s="32"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="14" t="s">
+      <c r="A64" s="23"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E64" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="E64" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="31"/>
-      <c r="B65" s="32" t="s">
+      <c r="A65" s="23"/>
+      <c r="B65" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C65" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E65" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="E65" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8" ht="24">
-      <c r="A66" s="31"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="14" t="s">
+      <c r="A66" s="23"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E66" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+      <c r="E66" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="B49:B62"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C56:C57"/>
@@ -2473,6 +2322,14 @@
     <mergeCell ref="B22:B48"/>
     <mergeCell ref="C22:C34"/>
     <mergeCell ref="C35:C48"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="B49:B62"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2492,77 +2349,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="222.75" customHeight="1">
-      <c r="A2" s="20">
+    <row r="2" spans="1:6" ht="263.25" customHeight="1">
+      <c r="A2" s="24">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="28" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-    </row>
-    <row r="4" spans="1:6" ht="268.5" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>122</v>
-      </c>
-    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:F3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>